--- a/Codelist Excel Files and Conversion Templates to XML/terminationOutcome.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/terminationOutcome.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes stating which stop rule actually governed the end of a rigid inclusion column's installation - design depth reached, or refusal. An as-built fact, distinct from the refusal criterion itself (a specification-side acceptance criterion cited by the construction activity, not a coded value). Used for the value of diggs:RIConstructionActivityType/diggs:terminationOutcome.</t>
+          <t>Codes stating which stop rule actually governed the end of a rigid inclusion column's installation - design depth reached, or refusal. An as-built fact, distinct from the refusal criterion itself (a specification-side acceptance criterion cited by the construction activity, not a coded value). Used for the value of diggs:RIColumnConstructionType/diggs:terminationOutcome.</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RIConstructionActivity/diggs:terminationOutcome</t>
+          <t>//diggs:RIColumnConstruction/diggs:terminationOutcome</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RIConstructionActivity/diggs:terminationOutcome</t>
+          <t>//diggs:RIColumnConstruction/diggs:terminationOutcome</t>
         </is>
       </c>
     </row>
